--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487920_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487920_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0533</v>
+        <v>3.9145</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7645</v>
+        <v>5.5083</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7112</v>
+        <v>-1.5938</v>
       </c>
       <c r="G2" t="n">
         <v>3.5673</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7398</v>
+        <v>0.601</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0745</v>
+        <v>0.8182</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3346</v>
+        <v>-0.2172</v>
       </c>
       <c r="V2" t="n">
         <v>-2.3351</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7259</v>
+        <v>3.4429</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9972</v>
+        <v>5.9197</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2713</v>
+        <v>-2.4768</v>
       </c>
       <c r="G3" t="n">
         <v>4.5587</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.019</v>
+        <v>-0.3021</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.901</v>
+        <v>0.0215</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.118</v>
+        <v>-0.3235</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8137</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8923</v>
+        <v>-0.218</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2626</v>
+        <v>0.415</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3703</v>
+        <v>-0.6329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7245</v>
+        <v>-0.0968</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4903</v>
+        <v>-0.1727</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2148</v>
+        <v>0.0759</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7411</v>
+        <v>0.634</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7188</v>
+        <v>0.5948</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4599</v>
+        <v>0.0392</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0166</v>
+        <v>-0.7308</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2284</v>
+        <v>-0.7675</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.245</v>
+        <v>0.0367</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.4974</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.249</v>
+        <v>-0.1212</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4133</v>
+        <v>-0.2191</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1643</v>
+        <v>0.0979</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>G. VERGARA HARBOE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4491</v>
+        <v>-0.413</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2426</v>
+        <v>0.0617</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6916</v>
+        <v>-0.4748</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0968</v>
+        <v>0.9326</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1727</v>
+        <v>0.3472</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0759</v>
+        <v>0.5854</v>
       </c>
       <c r="J5" t="n">
-        <v>0.634</v>
+        <v>2.7207</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5948</v>
+        <v>0.927</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0392</v>
+        <v>1.7937</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7308</v>
+        <v>-1.7881</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7675</v>
+        <v>-0.5798</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0367</v>
+        <v>-1.2083</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3523</v>
+        <v>0.0675</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3915</v>
+        <v>0.0029</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0391</v>
+        <v>0.0646</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. VERGARA HARBOE</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3333</v>
+        <v>-0.9853</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7117</v>
+        <v>0.6786</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6216</v>
+        <v>-1.6639</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9326</v>
+        <v>0.7245</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3472</v>
+        <v>-0.4903</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5854</v>
+        <v>1.2148</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7207</v>
+        <v>1.7411</v>
       </c>
       <c r="K6" t="n">
-        <v>0.927</v>
+        <v>-0.7188</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7937</v>
+        <v>2.4599</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7881</v>
+        <v>-1.0166</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5798</v>
+        <v>0.2284</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2083</v>
+        <v>-1.245</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8731</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8527</v>
+        <v>1.3713</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7705</v>
+        <v>1.8293</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0822</v>
+        <v>-0.4579</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4599</v>
+        <v>-0.5838</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4599</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. FIELDS</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4553</v>
+        <v>-1.1231</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4841</v>
+        <v>1.7203</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9394</v>
+        <v>-2.8434</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1625</v>
+        <v>-0.3655</v>
       </c>
       <c r="H7" t="n">
-        <v>0.454</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2915</v>
+        <v>0.4425</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6364</v>
+        <v>0.6756</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0421</v>
+        <v>0.0576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4739</v>
+        <v>-1.0411</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5881</v>
+        <v>-0.8655</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8858</v>
+        <v>-0.1755</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7411</v>
+        <v>0.2236</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6178</v>
+        <v>-0.1228</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1234</v>
+        <v>0.3464</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.4401</v>
+        <v>-1.3975</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.6701</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5686</v>
+        <v>-1.3162</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3336</v>
+        <v>-1.7861</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9021</v>
+        <v>0.4699</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3655</v>
+        <v>0.0097</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.5756</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4425</v>
+        <v>0.5854</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6756</v>
+        <v>0.2874</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0576</v>
+        <v>-0.3306</v>
       </c>
       <c r="L8" t="n">
         <v>0.618</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0411</v>
+        <v>-0.2777</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8655</v>
+        <v>-0.245</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1755</v>
+        <v>-0.0326</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4162</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2218</v>
+        <v>0.007</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2877</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3975</v>
+        <v>0.1238</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.565</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
+          <t>C. FIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9019</v>
+        <v>-1.4944</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1076</v>
+        <v>2.6799</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2057</v>
+        <v>-4.1743</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0097</v>
+        <v>0.1625</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5756</v>
+        <v>0.454</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5854</v>
+        <v>-0.2915</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2874</v>
+        <v>1.6364</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3306</v>
+        <v>1.0421</v>
       </c>
       <c r="L9" t="n">
-        <v>0.618</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2777</v>
+        <v>-1.4739</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.245</v>
+        <v>-0.5881</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0326</v>
+        <v>-0.8858</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5787</v>
+        <v>0.702</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3138</v>
+        <v>0.8135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2649</v>
+        <v>-0.1115</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1238</v>
+        <v>-4.4401</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1238</v>
+        <v>-4.6701</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2464</v>
+        <v>-2.0828</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.7148</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5736</v>
+        <v>-1.368</v>
       </c>
       <c r="G10" t="n">
         <v>-1.132</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1768</v>
+        <v>-0.0132</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1924</v>
+        <v>0.1505</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3692</v>
+        <v>-0.1637</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9376</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.586</v>
+        <v>-2.8104</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8091</v>
+        <v>-2.2914</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7769</v>
+        <v>-0.519</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3162</v>
+        <v>-0.8197</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5437</v>
+        <v>-1.1814</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7725</v>
+        <v>0.3617</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5974</v>
+        <v>-1.0442</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8169</v>
+        <v>-1.0834</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7805</v>
+        <v>0.0392</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7187</v>
+        <v>0.2245</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7268</v>
+        <v>-0.098</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9919</v>
+        <v>0.3225</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8325</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8977000000000001</v>
+        <v>-0.1988</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2015</v>
+        <v>-0.2067</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6962</v>
+        <v>0.0078</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6275</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.159</v>
+        <v>-2.9634</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4638</v>
+        <v>-1.8929</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-1.0705</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8197</v>
+        <v>-4.3162</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1814</v>
+        <v>-2.5437</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3617</v>
+        <v>-1.7725</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0442</v>
+        <v>-2.5974</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0834</v>
+        <v>-1.8169</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0392</v>
+        <v>-0.7805</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2245</v>
+        <v>-1.7187</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.098</v>
+        <v>-0.7268</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3225</v>
+        <v>-0.9919</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5474</v>
+        <v>0.5203</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3791</v>
+        <v>0.1177</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1683</v>
+        <v>0.4026</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.028099999999999</v>
+        <v>-6.049200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9.319500000000001</v>
+        <v>10.2983</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.3474</v>
+        <v>-16.3475</v>
       </c>
       <c r="G13" t="n">
         <v>3.2251</v>
@@ -1444,7 +1444,7 @@
         <v>15.0648</v>
       </c>
       <c r="K13" t="n">
-        <v>4.410699999999999</v>
+        <v>4.4107</v>
       </c>
       <c r="L13" t="n">
         <v>10.6543</v>
@@ -1456,7 +1456,7 @@
         <v>-5.1042</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.735300000000001</v>
+        <v>-6.7353</v>
       </c>
       <c r="P13" t="n">
         <v>-1.0406</v>
@@ -1468,10 +1468,10 @@
         <v>10.406</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8789</v>
+        <v>2.8574</v>
       </c>
       <c r="T13" t="n">
-        <v>2.233999999999999</v>
+        <v>3.2126</v>
       </c>
       <c r="U13" t="n">
         <v>-0.3551</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2965</v>
+        <v>2.8262</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9368</v>
+        <v>2.8695</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3597</v>
+        <v>-0.0432</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0069</v>
+        <v>2.8805</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8679</v>
+        <v>2.3646</v>
       </c>
       <c r="I14" t="n">
-        <v>2.139</v>
+        <v>0.516</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5868</v>
+        <v>3.7501</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1661</v>
+        <v>2.4177</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4207</v>
+        <v>1.3324</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5798</v>
+        <v>-0.8696</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2982</v>
+        <v>-0.0532</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2817</v>
+        <v>-0.8164</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
         <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0268</v>
+        <v>-0.0543</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0743</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1011</v>
+        <v>0.0157</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2445</v>
+        <v>2.6028</v>
       </c>
       <c r="E15" t="n">
-        <v>2.548</v>
+        <v>1.7225</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3036</v>
+        <v>0.8803</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8805</v>
+        <v>3.0069</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3646</v>
+        <v>0.8679</v>
       </c>
       <c r="I15" t="n">
-        <v>0.516</v>
+        <v>2.139</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7501</v>
+        <v>3.5868</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4177</v>
+        <v>1.1661</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3324</v>
+        <v>2.4207</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8696</v>
+        <v>-0.5798</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0532</v>
+        <v>-0.2982</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8164</v>
+        <v>-0.2817</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R15" t="n">
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6361</v>
+        <v>0.2796</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3915</v>
+        <v>-0.14</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2446</v>
+        <v>0.4195</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7098</v>
+        <v>2.1526</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1108</v>
+        <v>5.0036</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.401</v>
+        <v>-2.851</v>
       </c>
       <c r="G16" t="n">
         <v>0.09619999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.1111</v>
       </c>
       <c r="T16" t="n">
-        <v>0.593</v>
+        <v>0.4858</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1469</v>
+        <v>-0.5969</v>
       </c>
       <c r="V16" t="n">
         <v>1.7513</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3501</v>
+        <v>2.0297</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2969</v>
+        <v>1.047</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0532</v>
+        <v>0.9827</v>
       </c>
       <c r="G17" t="n">
         <v>-1.268</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.82</v>
+        <v>-0.1404</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9663</v>
+        <v>-0.2162</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1463</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>1.9813</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2775</v>
+        <v>1.6871</v>
       </c>
       <c r="E18" t="n">
-        <v>1.306</v>
+        <v>1.6275</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0285</v>
+        <v>0.0596</v>
       </c>
       <c r="G18" t="n">
         <v>0.4555</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.2461</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7829</v>
+        <v>-0.4615</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1273</v>
+        <v>0.2153</v>
       </c>
       <c r="V18" t="n">
         <v>1.0614</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.579</v>
+        <v>0.0639</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8156</v>
+        <v>-0.3138</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2366</v>
+        <v>0.3777</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.978</v>
+        <v>-1.1964</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0319</v>
+        <v>-0.3988</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0099</v>
+        <v>-0.7976</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3164</v>
+        <v>0.4529</v>
       </c>
       <c r="K19" t="n">
-        <v>0.62</v>
+        <v>0.4709</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6964</v>
+        <v>-0.018</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2944</v>
+        <v>-1.6494</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5881</v>
+        <v>-0.8697</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7063</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>1.325</v>
+        <v>0.2812</v>
       </c>
       <c r="T19" t="n">
-        <v>1.826</v>
+        <v>-0.2891</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.501</v>
+        <v>0.5703</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1051</v>
+        <v>-0.4776</v>
       </c>
       <c r="W19" t="n">
-        <v>2.795</v>
+        <v>-0.4776</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1885</v>
+        <v>-0.4059</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7423999999999999</v>
+        <v>1.6369</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5538999999999999</v>
+        <v>-2.0428</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1964</v>
+        <v>-0.978</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3988</v>
+        <v>0.0319</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7976</v>
+        <v>-1.0099</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4529</v>
+        <v>1.3164</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4709</v>
+        <v>0.62</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.018</v>
+        <v>0.6964</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6494</v>
+        <v>-2.2944</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8697</v>
+        <v>-0.5881</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-1.7063</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4568</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0287</v>
+        <v>0.3401</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7177</v>
+        <v>0.6473</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7464</v>
+        <v>-0.3072</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4776</v>
+        <v>2.1051</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4776</v>
+        <v>2.795</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7876</v>
+        <v>-0.6765</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2145</v>
+        <v>1.893</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0021</v>
+        <v>-2.5695</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3476</v>
@@ -2092,13 +2092,13 @@
         <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1507</v>
+        <v>-0.0396</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3972</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.548</v>
+        <v>-0.1154</v>
       </c>
       <c r="V21" t="n">
         <v>3.5026</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4532</v>
+        <v>-1.1087</v>
       </c>
       <c r="E22" t="n">
         <v>0.8613</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3145</v>
+        <v>-1.97</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8743</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3895</v>
+        <v>-0.045</v>
       </c>
       <c r="T22" t="n">
         <v>0.3229</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7124</v>
+        <v>-0.3679</v>
       </c>
       <c r="V22" t="n">
         <v>-0.23</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.028100000000001</v>
+        <v>9.171199999999999</v>
       </c>
       <c r="E23" t="n">
         <v>16.3475</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.3195</v>
+        <v>-7.176200000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2252</v>
@@ -2218,7 +2218,7 @@
         <v>0.6937000000000002</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.9188</v>
+        <v>-3.918800000000001</v>
       </c>
       <c r="J23" t="n">
         <v>11.8397</v>
@@ -2248,13 +2248,13 @@
         <v>11.4464</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.879</v>
+        <v>0.2644</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3549999999999998</v>
+        <v>0.3549999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.234</v>
+        <v>-0.09079999999999994</v>
       </c>
       <c r="V23" t="n">
         <v>11.0916</v>
